--- a/홍보처_추천목록.xlsx
+++ b/홍보처_추천목록.xlsx
@@ -819,7 +819,11 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>horangee_fnb@naver.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1061,11 @@
           <t>0507-1355-1425</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>horangee_fnb@naver.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
@@ -1325,7 +1333,11 @@
           <t>031-753-2501</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>kti114@nate.com</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
@@ -1431,7 +1443,11 @@
           <t>010-2384-5850</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>grpp@daum.net</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
@@ -1748,7 +1764,11 @@
           <t>521-8275</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>seocho8275@naver.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
@@ -1986,7 +2006,11 @@
           <t>1877-5661</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>km.kim1@lottebobath.net</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +3012,11 @@
           <t>02-848-0100</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hmp0100@noksib.com</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
@@ -4384,7 +4412,11 @@
           <t>031-528-8899</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>toojeam8899@naver.com</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
@@ -5510,7 +5542,11 @@
           <t>032-612-0056</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>biglove0056@naver.com</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
@@ -7558,7 +7594,11 @@
           <t>032-710-6001</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>naeun6201@naver.com</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
@@ -9898,7 +9938,11 @@
           <t>031-760-3691</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>srcrecruit@naver.com</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
@@ -10632,7 +10676,11 @@
           <t>031-406-7777</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>sas9955@naver.com</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
@@ -13541,7 +13589,11 @@
           <t>02-526-0821</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mokhuri@hanmail.net</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
@@ -15007,7 +15059,11 @@
           <t>02-1833-7555</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>healbon2@gmail.com</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
@@ -16585,7 +16641,11 @@
           <t>032-327-0600</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>miraclecc@naver.com</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
@@ -18993,7 +19053,11 @@
           <t>02-1588-2915</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>dreamoriental@naver.com</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
@@ -20569,7 +20633,11 @@
           <t>031-665-7654</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>gaon_hb@naver.com</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
@@ -21294,7 +21362,11 @@
           <t>02-3496-3300</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>webmaster@kmi.or.kr</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
@@ -21362,7 +21434,11 @@
           <t>02-2112-5500</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>stone@snuh.org</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
@@ -21464,7 +21540,11 @@
           <t>02-590-1111</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>himi2@hanaromf.com; privacy@hanaromf.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>02-590-1255</t>
@@ -21714,7 +21794,11 @@
           <t>02-368-8114</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>webmaster@kmi.or.kr</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
@@ -21782,7 +21866,11 @@
           <t>02-3702-9000</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>webmaster@kmi.or.kr</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
@@ -21816,7 +21904,11 @@
           <t>02-590-1111</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>himi2@hanaromf.com; privacy@hanaromf.com</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>02-2158-7256</t>
@@ -21926,7 +22018,11 @@
           <t>031-231-0114</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>webmaster@kmi.or.kr</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
@@ -22773,7 +22869,11 @@
           <t>031-612-1512</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ptfood@ptfood.kr; juliet0928@nate.com</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>

--- a/홍보처_추천목록.xlsx
+++ b/홍보처_추천목록.xlsx
@@ -13,6 +13,8 @@
     <sheet name="한방병원(수도권)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="건강검진센터" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="로컬푸드직매장" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="온라인커뮤니티(밴드)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="공급처(B2B)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'건강원·건강식품점'!$A$1:$H$23</definedName>
@@ -20,6 +22,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'한방병원(수도권)'!$A$1:$H$303</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'건강검진센터'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'로컬푸드직매장'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'온라인커뮤니티(밴드)'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'공급처(B2B)'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -541,95 +545,131 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6. 온라인커뮤니티(밴드)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>활성 네이버 밴드·카페 — 공구 제안·체험단·운영진 제휴 채널</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7. 공급처(B2B)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>온라인 입점 플랫폼·친환경 유통·산후조리원 등 납품/입점 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>우선순위(G열) 기준 — 구매력 상위 지역</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1순위</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>서울 강남·서초·송파·용산 / 성남 분당(판교)·과천·하남·용인 수지·수원 영통(광교)·안양 동안(평촌)·화성 동탄 / 인천 연수(송도) 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2순위</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>서울 마포·성동·양천·영등포·종로 등 / 고양(일산)·부천·김포·수원·용인 기흥 등 / 인천 서구(청라)·부평·남동</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3순위</t>
+          <t>1순위</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>서울 강남·서초·송파·용산 / 성남 분당(판교)·과천·하남·용인 수지·수원 영통(광교)·안양 동안(평촌)·화성 동탄 / 인천 연수(송도) 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>서울 마포·성동·양천·영등포·종로 등 / 고양(일산)·부천·김포·수원·용인 기흥 등 / 인천 서구(청라)·부평·남동</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3순위</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>그 외 수도권 지역</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>데이터 출처</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>요양병원·한방병원</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>건강보험심사평가원(HIRA) 병원·약국 찾기 (공식 데이터, 전수)</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>건강원·검진센터·로컬푸드</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>웹 검색 교차 확인 (대표 업체 선별 수집)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>건강원·검진센터·로컬푸드</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>웹 검색 교차 확인 (대표 업체 선별 수집)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>밴드·공급처</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>웹 검색 교차 확인 — 밴드 멤버수·활동성은 검색 노출 기준이라 가입 전 재확인 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>이메일·팩스는 공공 데이터에 공개되지 않아 대부분 빈칸 — 전화/홈페이지 문의폼 활용 권장</t>
         </is>
@@ -22925,4 +22965,1782 @@
   <autoFilter ref="A1:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>커뮤니티명</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>멤버수</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>활동성 근거</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>비고(접근법)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>맘스홀릭베이비 (네이버 카페)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>육아 카페</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>약 320만명</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/imsanbu</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>국내 최대 육아 카페. 공식 광고·공동구매 게시판 상시 운영 (광고대행 모집공고로 확인)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>카페 공식 공구 입점(기획전+회원 쪽지 발송) — 출산·육아 가정의 미역국용 참기름·들기름 수요와 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>레몬테라스 (네이버 카페)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>리빙·살림 카페</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>미확인(네이버 대표 리빙 카페)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/remonterrace</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>전용 체험단 프로그램 상시 운영 — 쿠쿠 등 대기업 신제품 체험단 진행 이력 확인</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>체험단·배너 제휴로 살림 관심층(주부) 공략, 후기 콘텐츠 확보용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>82쿡</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>요리·생활 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>비공개(이용자 평균 연령 높음, 50대 중심 30~70대)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.82cook.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2002년 개설된 요리 출발 커뮤니티, 2026년 현재도 활발 운영</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>중장년 여성 비중이 높아 전통 착유 기름과 타깃 일치 — 배너/장터 제휴 문의</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>우리농산물직거래장터</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>직거래 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@officework-mail</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>다음·네이버 카페와 유튜브를 함께 운영하는 수수료 무료 직거래 장터로 검색 확인</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>농산가공품 직거래 게시 가능 여부 운영진 문의 — 무료 채널이라 테스트 비용 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>네이버 밴드 — 앱 내 직접 발굴 (가이드)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>밴드</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://band.us/discover</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>밴드는 외부 검색엔진에 거의 인덱싱되지 않아 외부에서 멤버수·활동성 검증 불가 — 앱 내 검색이 유일하게 정확한 방법</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>앱에서 '공동구매', '농산물 직거래', '5060', '산악회', '건강식품', '귀농귀촌' 검색 → 멤버수·최근 게시일 확인 → 리더(운영진)에게 쪽지로 공구/협찬 제안. 멤버 1만+ 공개 밴드 우선</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>네이버 성과형 디스플레이 광고(GFA) — 밴드 지면</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>밴드 광고</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://gfa.naver.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>네이버 공식 광고 플랫폼으로 밴드 피드·새소식 지면에 광고 집행 가능 (운영 가이드 영상 확인)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>개별 밴드 가입 없이 밴드 이용자(40~60대 비중 높음)에게 연령·지역 타겟 광고 — 소액 테스트 후 확장 권장</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>공급처명</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>전화번호</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>입점·안내 페이지</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>입점·납품 방법</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>비고(요건·특징)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>마켓컬리(컬리)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.kurly.com/introduce/sustainable-distribution/joint-growth</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>컬리 홈페이지 하단 '입점신청'(입점 문의 폼) 제출 → MD 검토 후 개별 연락, 직매입 중심. 오픈마켓(3P) 셀러는 파트너 오피스(3p-partner.kurly.com)에서 별도 신청.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>사업자등록증 등 기본 서류 필요. 프리미엄 식품 큐레이션 성향이라 저온압착·전통착유 스토리가 유리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>오아시스마켓</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1577-0098</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>oasis@oasis.co.kr</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://tmon-ad.oasis.co.kr/contactUs/tmon/contactMain</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>입점상담 페이지에서 회원가입 후 온라인 신청서 작성 → MD 검토·대면 미팅 → 상품 품질평가·내부심사 → 계약 체결.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>친환경·유기농 새벽배송 전문. '업계 최저 수수료, 구매확정 후 익일 정산' 표방. 본사 경기 성남시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>카카오메이커스</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://makers-partner-center.kakao.com/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>메이커스 파트너센터에서 입점(상품) 제안서 제출 → 내부 검토 및 오프라인 미팅 → 입점 파트너 선정.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>주문 후 생산(공동주문) 방식. 농축수산 가공식품 제조사 대상 '제가버치' 프로젝트 운영, 선정 시 콘텐츠 제작·마케팅 지원.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>우체국쇼핑 (한국우편사업진흥원)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>042-609-4298</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>b2bscm@posa.or.kr</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://mall.epost.go.kr/fo/center/centerGuideCustStat.do</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>회사소개·취급 상품군을 이메일로 접수 → 담당 MD가 입점신청서 양식 회신 → 서류심사 → 현지실사 → 상품심사 → 등록·판매.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>전통식품관 보유, 전통식품 인증·식품명인 지정업체 우대. 가공식품은 품목제조신고·공장등록증 등 필요. 농어촌 중소 생산자 판로 지원 성격의 공공 쇼핑몰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>아이디어스(idus)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://debut.idus.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>'작가의 시작'(debut.idus.com)에서 입점 신청 → 브랜드 소개서·제작과정/결과물 사진 제출 → 심사(수일~4주) 후 판매 개시.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>식품은 '수공정 포함' 기준이 엄격해 전통 방식 착유 공정이 오히려 강점. 초기 입점비 없음, 판매 수수료 차감 구조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>판판대로 (한국중소벤처기업유통원)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>02-6678-9714</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://fanfandaero.kr/portal/readGuidanceDistb.do?sportBsnsNo=distb190</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>회원가입 → 지원사업·상품 선택, 서류 등록 후 온라인 신청(정책매장 입점은 연중 접수) → 선정 시 입점 연계.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>중기부 산하 통합 판로지원 플랫폼. 백화점·대형마트 입점상담회, 오프라인 기획전 공고 수시 게시. 중소기업확인서 기본 요건.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>동반성장몰</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1522-6009</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://support.dongbanmall.com/entrance</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>판판대로 통해 입점 신청 → 서류평가·상품선정위원회 심사 → 전자계약·통합상품코드 발급 → 상품 등록, MD 승인 후 노출.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>대기업·공공기관 임직원 복지포인트 쇼핑몰(B2B2E)이라 명절 선물세트 수요 큼. 국내 제조 중소기업만 가능, 타 온라인몰 대비 저가·무료배송 정책 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>경기도주식회사 (코리아경기도)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kgc@kgcbrand.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.kgcbrand.com/KGCBrand/businessNoticeList.do</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>사업공고 게시판에서 유통채널 입점업체 모집 공고 확인 → 입점신청서 이메일 제출(연중 상시) → 심사 후 온·오프라인 채널 연계.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>경기도 내 본사 또는 공장 소재 중소기업·소상공인·협동조합 대상. 마케팅·유통 대행 지원형 공공기업.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>마켓경기 (경기도농수산진흥원)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/marketgyeonggi/notice/detail?id=2001667441</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>네이버 스마트스토어 '마켓경기' 공지의 원클릭 간편입점 신청서 제출 → 진흥원 검토 후 입점.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>경기도 대표 농식품 온라인몰. 경기도 농가·농식품 경영체 대상(2026.3 공고 기준). 운영기관 경기도농수산진흥원(gafi.or.kr).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>와디즈 (펀딩)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>온라인 입점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1661-9056</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.wadiz.kr/web/wsub/openfunding/reward</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>'프로젝트 오픈 신청'으로 리워드 프로젝트 개설 → 메이커 스튜디오에서 심사팀 피드백 반영 → 승인 후 7~60일 펀딩 진행.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>푸드 카테고리 활성. 신제품(선물세트, 첫 출시 기름) 테스트와 초기 자금 확보에 적합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>한살림 (한살림연합)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>친환경 유통</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1661-0800</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>http://www.hansalim.or.kr/</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>조합원상담실(1661-0800) 또는 장보기 사이트 문의로 신규 물품 제안 접수 → 자체 물품 기준 심사 후 취급 여부 결정.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>전국 30개 지역생협·233개 매장(2026.4 기준). 국산 원료·친환경 등 취급 기준 엄격 — 원료 산지 증빙 준비 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>자연드림 (아이쿱생협)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>친환경 유통</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1577-6009</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>icoopmall@icoop.or.kr</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://icoop.or.kr/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>입점문의 이메일 또는 상담센터로 물품 공급 제안 → 내부 검토 후 협의.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>아이쿱생협 매장·온라인 브랜드. 자체 생산 클러스터 보유라 외부 공급은 원료·인증 기준 충족이 관건.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>초록마을</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>친환경 유통</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02-6715-7116</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.choroc.com/</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>본사 또는 고객센터(080-023-0023) 경유 MD 상품 제안 → 안전성 검사 등 자체 기준 심사 후 납품 계약.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>주의: 2025년 7월 기업회생절차 개시, 2026년 현재 매각(M&amp;A) 진행 중 — 신규 거래 조건 확인 필수. 전국 200여 개 매장 영업은 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>올가홀푸드 (풀무원 계열)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>친환경 유통</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>서울 송파구</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>02-2104-0114</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.orga.co.kr/</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>본사(송파구 중대로 168) 상품 담당 부서로 입점 제안 → 친환경 기준 검토 후 매장·온라인 입점.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>풀무원 계열 친환경 전문점(직영점·숍인숍·온라인). 친환경/유기 인증 상품 위주 MD. 카카오톡채널로도 문의 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>트리니티 산후조리원 (체인)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>서울 용산구</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>02-6985-3787</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>trinitycare5993@gmail.com</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://trinitycare.co.kr/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울드래곤시티(용산)·삼성·강동송파·판교 4개 지점 운영 체인. 본점 연락처로 산모식 식자재(미역국용 참기름·들기름) 납품 제안 및 샘플 제공.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>호텔형 프리미엄 체인이라 지점 통합 구매 협의 가능성. 마케팅 제휴 창구(contact@momcho.co.kr) 별도.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>궁 산후조리원 강남본원</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>02-555-9550</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mkt@goongs.com</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://gangnam.goongs.com/</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>대표전화 또는 이메일로 산모식 식자재 납품 상담 요청 → 주방(조리)팀 검토 후 거래.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>역삼동 소재 고급 산후조리원. 산모 맞춤식단 운영으로 국산 참기름·들기름 수요 적합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헤리티지 산후조리원 (청담)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.heritagecenter.co.kr/</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>홈페이지·카카오톡채널로 상담 접수 후 식자재 납품 제안.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>센트럴·청담(2호점) 등 복수 지점 운영 프리미엄 브랜드. 대표전화 비공개로 채널 문의 우선.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>마리더블레스 산후조리원 청담</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02-3471-2233</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>http://theblesscd.kr/</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>대표전화 또는 홈페이지 전화상담 신청을 통해 식자재 납품 상담.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>청담동 70-4 소재 프리미엄 산후조리원. 산모식 직영 조리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>분당차여성병원 산후조리원 (차병원 계열)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>경기 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>031-780-2998</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://bundangwoman.chamc.co.kr/obstetrics/postpartumCare_introduction_sub.cha</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>산후조리원 직통(031-780-2997~8) 문의하되, 병원 연계형이라 식자재는 병원 영양팀/구매 부서 경유 제안이 현실적.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>차병원그룹 병원 부속 대형 조리원. HACCP·시험성적서 등 서류 요구 가능성 높음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>디에르 산후조리원</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>경기 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>031-717-7787</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>http://dehercare.com/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>대표전화로 식자재 납품 상담 요청.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>분당 정자동(더샵스타파크) 소재 프리미엄 조리원.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>분당제일산후조리원 (분당제일여성병원)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>산후조리원</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>경기 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>031-703-1004</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.bundangcheil.com/postpartum_about.php</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>조리원 직통전화로 납품 상담, 병원 연계형이라 영양·급식 담당 경유 협의.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>서현역 인근 여성병원 부속 조리원.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>진이찬방 (진이푸드)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>반찬업체</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>인천 미추홀구</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1577-7241</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>jinifood01@hanmail.net</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://jinifood.co.kr/</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>본사 대표전화·이메일로 원재료(참기름·들기름) 납품 제안 → 본사 구매 담당 검토 후 공장 공급 계약.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>전국 100여 개 가맹점 반찬 프랜차이즈. HACCP 인증 본사 공장에서 완제품 제조·공급하는 구조라 기름류 대량 수요 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>국선생 (홈스푸드)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>반찬업체</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>서울 송파구</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>02-2203-9455</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.homesfood.co.kr/</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>본사(송파구 송이로 87) 대표전화로 식자재 납품 제안 → 구매 담당 협의.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>한우·무농약·국내산 식재료 콘셉트의 프리미엄 반찬 프랜차이즈 — 국산 전통 착유 기름과 콘셉트 부합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>오레시피 (도들샘)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>반찬업체</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>경북 경산시</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1899-4330</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>twhan3079@hanmail.net</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://orecipe.co.kr/</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>본사 대표번호·이메일로 원료 납품 제안 → 본사 공장(밀키트 일괄 생산) 구매 협의.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>전국 200여 개 가맹점 반찬 프랜차이즈. 전 제품을 본사에서 밀키트 형태로 가맹점에 공급해 본사 일괄 구매 구조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>신세계백화점 (협력회사 상담실)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.shinsegae.com/company/partner/guide.do</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>협력회사 상담실에서 온라인 입점상담 신청(사업자등록증 등 첨부) → 바이어 상담·품평회 → 입점 확정 시 파트너포탈 등록·전자계약.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>접수 후 약 3일 내 처리 결과 안내. 식품관 입점은 품평회 통과가 핵심 — 선물세트 시제품 준비 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>현대백화점 (상품본부)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://partners.ehyundai.com/ghh/</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>상품본부 홈페이지에서 임시회원 가입(휴대폰 인증, 7일 유효) → 입점상담 신청·Q&amp;A → 입점 결정 시 전자계약으로 협력사 등록.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>협력사 포털 H-Partners 기반. 중소기업유통센터 주관 현대백화점 기획전(판판대로 공고) 경유 입점 경로도 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>롯데백화점 (MD본부)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1577-0001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://buying.lotteshopping.com/counsel/counsel_index.jsp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MD본부 홈페이지에서 입점상담 신청(필수) → 바이어 상담·1차 평가 → 품평회 → 입점 확정·협력회사 평가.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>상품설명서·샘플·사업자등록증·회사개요 등 준비. 품평회는 연중 진행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>현대이지웰 (복지몰)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>선물세트 B2B</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1660-0011</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ezhelp@hyundaiezwel.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://partner.ezwel.com/partner/enterInfo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>협력사 지원센터에서 입점 신청 → 입점심사 → 입점상담 → 전자계약 체결 후 어드민 계정 발급·상품 등록.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>국내 최대급 임직원 복지포인트 몰(현대백화점그룹). 명절 기업 선물세트 수요가 큰 B2B2E 채널.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>베네피아 (SK엠앤서비스)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>선물세트 B2B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1566-9955</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.benepia.co.kr/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>사이트 하단 '입점/제휴문의' 폼으로 상품 입점 제안 → 담당 MD 검토 후 협의.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>약 3,700개 고객사·임직원 130만 명 복지 플랫폼. 명절 선물세트·식품 특판 수요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>아이마켓코리아</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>선물세트 B2B</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1544-8882</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.imarketkorea.com/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>홈페이지 '공급사 가입' 신청 → 담당자 승인 후 ID 발급 → 영업팀과 품목(명절 선물세트 특판 등) 협의.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>대기업 구매대행(B2B) 전문. 임직원 특가몰·명절 선물세트 특판 채널 보유.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>이마트</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>대형마트</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://store.emart.com/storeEntry/storeEntry_intro.do</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>홈페이지 '신규 입점·거래 제안'으로 상품 입점 제안 접수 → 담당 바이어 검토 후 연락. 상품매입부문 협력회사 상담실 별도 운영.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>신세계 계열. 중소기업 구매상담회 등 판로지원 프로그램 병행 — 판판대로 상담회 공고와 연계 활용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>롯데마트</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>대형마트</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://partner.lottemart.com/epc/edi/srm/SRMSTP0010.do</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>파트너 사이트 '입점상담 신청' 제출 → MD 검토 → 품평 → 거래 계약.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>입점상담 절차가 온라인으로 정형화되어 있어 소규모 제조사도 접근 용이.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>홈플러스</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>대형마트</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>02-2656-9022</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://corporate.homeplus.co.kr</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>기업 사이트의 상품 입점상담 신청 + 파트너센터(partners.homeplus.co.kr) 사업자 인증 후 입점 절차 진행.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>주의: 2025년 3월 기업회생절차 신청 — 거래 조건·대금 결제 안정성 확인 후 진행 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>이마트에브리데이</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SSM(슈퍼)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://ecrt.emarteveryday.co.kr/</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>이마트 입점 제안 채널과 에브리데이 협력회사 시스템(ECRT) 경유로 상품 제안.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>근린 슈퍼 채널 — 가정용 소용량 참기름·들기름 적합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GS리테일 (GS25·GS더프레시)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>편의점·SSM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1833-9779</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>http://www.gsretail.com/gsretail/ko/etc/partnership-index</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>GS리테일 '입점상담' 페이지에서 상품 입점 제안 접수 → 카테고리 MD 검토.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>편의점(GS25)과 슈퍼(GS더프레시)를 한 창구로 제안 가능 — 소포장·명절 선물세트 기획 유리. 전화는 GS더프레시 고객센터.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>농협하나로유통 (하나로마트)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>마트(농협)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>서울 마포구</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>02-2022-4500</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.nhhanaro.co.kr</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>본사(마포 농협신촌복합빌딩) 신규계약 상담 채널로 입점 제안. 양재 하나로클럽 등은 농협유통(02-3498-1000) 별도.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>국산 농산가공품 정체성과 부합도 최고 채널. 6차산업 인증 사업자는 하나로마트 입점지원 사업 활용 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CJ프레시웨이</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>식자재유통·급식</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>02-2149-6114</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.cjfreshway.com</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>홈페이지 문의 채널로 상품 공급 제안 → 카테고리 구매(소싱) 담당 연결.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>전국 급식·외식 식자재 공급 최대급 — 성사 시 물량 크지만 단가·생산능력 대응 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>삼성웰스토리</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>식자재유통·급식</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://srm.welstory.com</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SRM 협력회사 지원시스템에서 신규 협력회사 등록 신청 → 심사 후 거래.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>대기업 급식 1위권 — HACCP 등 인증·품질 심사 엄격, 시험성적서 준비 필수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>아워홈</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>식자재유통·급식</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.ourhome.co.kr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>홈페이지 협력회사/문의 채널로 공급 제안 → 구매 담당 검토.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>급식·식재 대기업. 병원·기업 급식 식자재로 들기름 수요 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>장보고식자재마트</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>식자재마트</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>대구·경북 중심</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>http://www.jangboja.com</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>본사 구매팀에 상품 입점 제안 (직거래 주문 시스템 jangbogopick.co.kr 운영).</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>전국구 식자재마트 체인 중 하나 — 자영업자(식당) 고객 비중 높아 업소용 대용량 적합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>세계로마트</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>식자재마트</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>서울 도봉구</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>본사(도봉구 도당로 75) 구매 담당으로 납품 제안.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>수도권 포함 전국 식자재마트 체인(1999년 설립). 업소용 식자재 채널.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>고속도로 휴게소 (한국도로공사)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>휴게소·특산품</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://ebid.ex.co.kr/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>상시 모집이 아닌 공모·입찰 방식 — 도로공사 전자입찰(ebid.ex.co.kr)과 휴게소 운영사 공고로 입점. 지역특산품 매장은 별도 공모.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>한국고속도로휴게시설협회(hsa.or.kr) 공고 병행 확인. 선물용 전통식품과 궁합 좋은 채널.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H43"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/홍보처_추천목록.xlsx
+++ b/홍보처_추천목록.xlsx
@@ -22,8 +22,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'한방병원(수도권)'!$A$1:$H$303</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'건강검진센터'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'로컬푸드직매장'!$A$1:$H$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'온라인커뮤니티(밴드)'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'공급처(B2B)'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'온라인커뮤니티(밴드)'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'공급처(B2B)'!$A$1:$H$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22973,7 +22973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23019,197 +23019,421 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>맘스홀릭베이비 (네이버 카페)</t>
+          <t>네이버 밴드 (플랫폼 자체)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>육아 카페</t>
+          <t>① 광고 타깃</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>약 320만명</t>
+          <t>MAU 1,738만(2025.2)~1,924만(2024 연평균)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/imsanbu</t>
+          <t>https://band.us</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>국내 최대 육아 카페. 공식 광고·공동구매 게시판 상시 운영 (광고대행 모집공고로 확인)</t>
+          <t>검증: 40·50대 비중 53.27%로 전 SNS 중 최고(머니투데이·테크M 2025). 당근보다 이용자 많은 2위권 SNS(한경 2024). 등산·동호회·동창회·육아 소모임 중심</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>카페 공식 공구 입점(기획전+회원 쪽지 발송) — 출산·육아 가정의 미역국용 참기름·들기름 수요와 직결</t>
+          <t>★중장년 타깃의 핵심 매체. 개별 밴드는 외부 크롤링 전면 차단(403)이라 멤버수 직접 확인 불가 → 아래 ②광고/③공구벤더/④자체운영 3트랙으로 접근</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>레몬테라스 (네이버 카페)</t>
+          <t>네이버 성과형디스플레이광고(GFA) — 밴드 피드 지면</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리빙·살림 카페</t>
+          <t>② 광고 집행</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>미확인(네이버 대표 리빙 카페)</t>
+          <t>밴드 전체 이용자 도달</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/remonterrace</t>
+          <t>https://gfa.naver.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>전용 체험단 프로그램 상시 운영 — 쿠쿠 등 대기업 신제품 체험단 진행 이력 확인</t>
+          <t>검증: 광고그룹 '게재위치 &gt; 네이버패밀리매체 &gt; 피드영역' 선택 시 밴드 피드 노출. 공식 운영 가이드 존재</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>체험단·배너 제휴로 살림 관심층(주부) 공략, 후기 콘텐츠 확보용</t>
+          <t>개별 밴드 가입 없이 연령·성별·지역·관심사·구매의도·맞춤타깃으로 밴드 이용자에 노출. CPM/CPC 입찰형, 소액 테스트 후 확장 권장. 식품에 가장 빠른 진입로</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>82쿡</t>
+          <t>BAND 광고 상품(소식·풀스크린 등) 소개서</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>요리·생활 커뮤니티</t>
+          <t>② 광고 집행</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>비공개(이용자 평균 연령 높음, 50대 중심 30~70대)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.82cook.com</t>
+          <t>https://ssl.pstatic.net/cmstatic/ad_guide/native_catalog/ko/native_catalog_6.6.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2002년 개설된 요리 출발 커뮤니티, 2026년 현재도 활발 운영</t>
+          <t>검증: 네이버 공식 광고 상품 카탈로그 PDF(23p) — 밴드 네이티브 광고 지면·타깃·과금 안내</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>중장년 여성 비중이 높아 전통 착유 기름과 타깃 일치 — 배너/장터 제휴 문의</t>
+          <t>스마트채널/피드/풀스크린 등 상품별 단가·규격 확인용 공식 자료. 대행 없이 직접 집행 가능</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리농산물직거래장터</t>
+          <t>온라인유통센터 (onumall)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>직거래 커뮤니티</t>
+          <t>③ 공구 벤더</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>제조·유통 45개사 협동조합</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@officework-mail</t>
+          <t>https://story.kakao.com/ch/onumall</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>다음·네이버 카페와 유튜브를 함께 운영하는 수수료 무료 직거래 장터로 검색 확인</t>
+          <t>검증: 카카오스토리+네이버밴드 공동구매를 진행하는 유통 협동조합으로 검색 확인</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>농산가공품 직거래 게시 가능 여부 운영진 문의 — 무료 채널이라 테스트 비용 없음</t>
+          <t>★자체 밴드 없이 진입하는 최선책 — 이미 채널을 가진 공구 조직에 제품을 공급. 카카오스토리 채널로 입점·공급 문의</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>네이버 밴드 — 앱 내 직접 발굴 (가이드)</t>
+          <t>아이보스 — 공동구매 대행/벤더 게시판</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>밴드</t>
+          <t>③ 공구 벤더</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>국내 최대 온라인마케팅 커뮤니티</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://band.us/discover</t>
+          <t>https://www.i-boss.co.kr/ab-1958</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>밴드는 외부 검색엔진에 거의 인덱싱되지 않아 외부에서 멤버수·활동성 검증 불가 — 앱 내 검색이 유일하게 정확한 방법</t>
+          <t>검증: '카스/밴드/맘카페 벤더 구함', '공구 벤더 제안' 등 식품 포함 의뢰글이 상시 게시(연매출 200억 업체 모집글 등)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>앱에서 '공동구매', '농산물 직거래', '5060', '산악회', '건강식품', '귀농귀촌' 검색 → 멤버수·최근 게시일 확인 → 리더(운영진)에게 쪽지로 공구/협찬 제안. 멤버 1만+ 공개 밴드 우선</t>
+          <t>'대행의뢰-대행컨설팅' 게시판에 공급 제안글을 직접 등록하거나 모집글에 컨택. 밴드 보유 벤더와 매칭</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>네이버 성과형 디스플레이 광고(GFA) — 밴드 지면</t>
+          <t>크몽 — 공동구매 셀러/인플루언서 리스트</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>밴드 광고</t>
+          <t>③ 공구 벤더</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>셀러 1,500+ 리스트</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://kmong.com/search?type=gigs&amp;keyword=공동구매%20셀러</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>검증: 현직 공구 벤더가 정리한 밴드·카스 셀러 1500명 리스트 등 거래 활발</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>밴드/카스 공구 셀러 연락처 패키지 구매 후 직접 공급 제안. 소량으로 빠르게 테스트 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>카카오 비즈니스 공식 대행사 리스트</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>③ 공구 벤더</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://gfa.naver.com</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>네이버 공식 광고 플랫폼으로 밴드 피드·새소식 지면에 광고 집행 가능 (운영 가이드 영상 확인)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>개별 밴드 가입 없이 밴드 이용자(40~60대 비중 높음)에게 연령·지역 타겟 광고 — 소액 테스트 후 확장 권장</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://kakaobusiness.gitbook.io/main/partner/list</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>검증: 2026년판 공식 대행사 명단(가나다순) 운영 — 카카오스토리 공구 연계 대행 탐색용</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>검증된 대행사를 통해 카스+밴드 동시 공구 집행. 밴드와 사용자층 겹치는 카스 공구 병행 효율적</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>맘스홀릭베이비 (네이버 카페)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>④ 대형 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>약 320만명</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/imsanbu</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>검증: 국내 1위 육아 카페, 공식 광고·공동구매 게시판 상시 운영(광고대행 모집공고 확인)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>공식 공구(기획전+회원 쪽지 발송). 출산·육아 가정의 미역국용 참기름·들기름 수요 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>레몬테라스 (네이버 카페)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>④ 대형 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>네이버 대표 리빙카페(수백만)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/remonterrace</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>검증: 전용 체험단 프로그램 상시 운영 — 쿠쿠 등 대기업 신제품 체험단 진행 이력</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>체험단·배너 제휴로 살림 관심 주부층 공략, 후기 콘텐츠 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>82쿡</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>④ 대형 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>비공개(이용자 평균연령 높음)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.82cook.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>검증: 2002년 개설 요리 출발 커뮤니티, 주 연령층 50대(30~70대), 2026년 현재도 활발</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>중장년 여성 비중 높아 전통 착유 기름과 타깃 일치. 배너/장터 제휴 문의</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>우리농산물직거래장터</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>④ 대형 커뮤니티</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@officework-mail</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>검증: 다음·네이버 카페+유튜브 병행 운영하는 수수료 무료 직거래 장터</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>농산가공품 직거래 게시 가능 여부 운영진 문의 — 무료라 테스트 비용 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>밴드 앱 내 직접 발굴 (실행 가이드)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>⑤ 자체 발굴</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://band.us/discover</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>밴드는 외부 검색 인덱싱을 막아 앱 내 검색이 멤버수·활동성 확인의 유일한 정확 경로</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>앱에서 '공동구매·농산물 직거래·5060·산악회·텃밭·건강식품·귀농귀촌' 검색 → 멤버 1만+ 공개·활동 밴드 선별 → 리더에게 쪽지로 협찬/공구 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>밴드 마켓 (자체 상점 개설)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>⑤ 자체 운영</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://band.us</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>밴드 내 커머스(밴드 마켓) 기능으로 직접 상점 개설·주문 접수 가능</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>단골 확보 후 직접 공구 운영. 초기엔 ②광고로 밴드 유입 → 자체 밴드 멤버화하는 조합이 효과적</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23220,7 +23444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -24739,8 +24963,68 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>집반찬연구소 (산남촌)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>반찬업체</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.zipbanchan.co.kr/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>카카오톡채널(_mKhxmd) 또는 홈페이지 고객센터로 원료(참기름·들기름) 납품 제안 → 구매 담당 협의.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>프리미엄 수제반찬 1위권. 롯데홈쇼핑 입점 규모 — 반찬 제조에 기름류 상시 대량 수요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>프런트9 (마이쿡푸드)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>반찬업체</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.front9.co.kr/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>홈페이지·전화로 B2B/대량주문 문의 창구 운영 — 원료 공급 제안 접수.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>전국 배송 수제반찬·구독 플랫폼. 단체·기업·대량주문 응대하므로 식재 공급 협의 가능.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>